--- a/data/Analyse15.xlsx
+++ b/data/Analyse15.xlsx
@@ -781,11 +781,11 @@
       </c>
       <c r="I2" s="8" t="n">
         <f aca="false">K2-H2</f>
-        <v>3.36</v>
+        <v>4.36</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="8" t="n">
-        <v>14.9</v>
+        <v>15.9</v>
       </c>
       <c r="L2" s="8" t="n">
         <f aca="false">N2-K2</f>
@@ -793,19 +793,19 @@
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="8" t="n">
-        <v>19.64</v>
+        <v>20.64</v>
       </c>
       <c r="O2" s="8" t="n">
         <f aca="false">Q2-N2</f>
-        <v>6.77</v>
+        <v>4.77</v>
       </c>
       <c r="P2" s="7"/>
       <c r="Q2" s="8" t="n">
-        <v>26.41</v>
+        <v>25.41</v>
       </c>
       <c r="R2" s="8" t="n">
         <f aca="false">Q2+S2*14/35</f>
-        <v>28.522</v>
+        <v>27.522</v>
       </c>
       <c r="S2" s="8" t="n">
         <f aca="false">U2-Q2</f>
@@ -813,7 +813,7 @@
       </c>
       <c r="T2" s="7"/>
       <c r="U2" s="8" t="n">
-        <v>31.69</v>
+        <v>30.69</v>
       </c>
       <c r="V2" s="8" t="n">
         <f aca="false">X2-U2</f>
@@ -821,7 +821,7 @@
       </c>
       <c r="W2" s="7"/>
       <c r="X2" s="8" t="n">
-        <v>36.96</v>
+        <v>35.96</v>
       </c>
       <c r="Y2" s="8" t="n">
         <f aca="false">AA2-X2</f>
@@ -829,7 +829,7 @@
       </c>
       <c r="Z2" s="7"/>
       <c r="AA2" s="8" t="n">
-        <v>42.36</v>
+        <v>41.36</v>
       </c>
       <c r="AB2" s="8" t="n">
         <f aca="false">AD2-AA2</f>
@@ -837,11 +837,11 @@
       </c>
       <c r="AC2" s="7"/>
       <c r="AD2" s="8" t="n">
-        <v>47.91</v>
+        <v>46.91</v>
       </c>
       <c r="AE2" s="8" t="n">
         <f aca="false">AG2-AD2</f>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AF2" s="7"/>
       <c r="AG2" s="8" t="n">
@@ -856,15 +856,15 @@
       </c>
       <c r="AJ2" s="8" t="n">
         <f aca="false">R2</f>
-        <v>28.522</v>
+        <v>27.522</v>
       </c>
       <c r="AK2" s="8" t="n">
         <f aca="false">AI2-R2</f>
-        <v>31.148</v>
+        <v>32.148</v>
       </c>
       <c r="AL2" s="8" t="n">
         <f aca="false">AK2-AJ2</f>
-        <v>2.626</v>
+        <v>4.62599999999999</v>
       </c>
       <c r="AM2" s="7"/>
       <c r="AN2" s="7"/>
